--- a/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
+++ b/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\OneDrive\Desktop\Input Data for India 2.0\land\FoFObE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\land\FoFObE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BBC6E8-B97F-4CCB-9CF9-2680728DCE5E}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D0EA2B-02FF-453F-9596-BFD3D1EA0E4A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9150" yWindow="690" windowWidth="29520" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
+    <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="FoFObE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -22,7 +22,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>FoFObE Fraction of Forests Owned by Entity</t>
   </si>
@@ -38,118 +41,73 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>National Forest</t>
+  </si>
+  <si>
+    <t>Other public</t>
+  </si>
+  <si>
+    <t>Forest industry</t>
+  </si>
+  <si>
+    <t>Other private</t>
+  </si>
+  <si>
+    <t>Timber land</t>
+  </si>
+  <si>
+    <t>Reserved forest</t>
+  </si>
+  <si>
+    <t>Other forest</t>
+  </si>
+  <si>
+    <t>U.S.</t>
+  </si>
+  <si>
+    <t>Ownership of Forest Land (million hectares)</t>
+  </si>
+  <si>
+    <t>U.S. Forest Service</t>
+  </si>
+  <si>
+    <t>U.S. Forest Facts and Historical Trends</t>
+  </si>
+  <si>
+    <t>http://www.fia.fs.fed.us/library/briefings-summaries-overviews/docs/ForestFactsMetric.pdf</t>
+  </si>
+  <si>
+    <t>Page 6</t>
+  </si>
+  <si>
     <t>government</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Total Recorded Forest Land</t>
-  </si>
-  <si>
-    <t>Recorded Forest Land in "000" ha (2000)</t>
-  </si>
-  <si>
-    <t>Recorded Forest under Private Ownership</t>
-  </si>
-  <si>
-    <t>Forest Department</t>
-  </si>
-  <si>
-    <t>Revenue Department</t>
-  </si>
-  <si>
-    <t>Corporate/Communities</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Public Owners of un-classed Forest</t>
-  </si>
-  <si>
-    <t>Owners of un-classed Forest</t>
-  </si>
-  <si>
-    <t>Private Owners</t>
-  </si>
-  <si>
-    <t>Public Owners</t>
-  </si>
-  <si>
-    <t>Type of Ownership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public </t>
-  </si>
-  <si>
-    <t>Private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other or Unspecified </t>
-  </si>
-  <si>
-    <t>Ownership of Forests and Other Wooded Lands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An unclassed forest is defined as any forest land or waste land or any </t>
-  </si>
-  <si>
-    <t xml:space="preserve">other land “recorded” in land records as “forest” but not notified in </t>
-  </si>
-  <si>
-    <t xml:space="preserve">government gazette as “reserved” or “protected” forests under </t>
-  </si>
-  <si>
-    <t>Indian Forest Act.</t>
-  </si>
-  <si>
-    <t>hectares</t>
-  </si>
-  <si>
-    <t>percent</t>
-  </si>
-  <si>
-    <t>Food and Agriculture Organization of the United Nations</t>
-  </si>
-  <si>
-    <t>Forests Owned By Entity</t>
-  </si>
-  <si>
-    <t>http://www.fao.org/docrep/007/ae354e/AE354E10.htm#P587_26537</t>
-  </si>
-  <si>
-    <t>We assume all privately owned land is owned by industry</t>
-  </si>
-  <si>
-    <t>Table: Input for Global Reporting Table 2</t>
+    <t>The amount of government-owned forest is provided in the table.</t>
+  </si>
+  <si>
+    <t>We assume that all privately-owned forest used for timber land is owned</t>
+  </si>
+  <si>
+    <t>by industry, and half of the remaining privately-owned forest land is owned</t>
+  </si>
+  <si>
+    <t>by industry.  The remainder is owned by consumers.</t>
+  </si>
+  <si>
+    <t>foreign entities</t>
+  </si>
+  <si>
+    <t>labor and consumers</t>
   </si>
   <si>
     <t>Fraction of Forest Owned (dimensionless)</t>
   </si>
   <si>
-    <t>nonenergy industries</t>
-  </si>
-  <si>
-    <t>labor and consumers</t>
-  </si>
-  <si>
-    <t>foreign entities</t>
-  </si>
-  <si>
-    <t>electricity suppliers</t>
-  </si>
-  <si>
-    <t>coal suppliers</t>
-  </si>
-  <si>
-    <t>natural gas and petroleum suppliers</t>
-  </si>
-  <si>
-    <t>biomass and biofuel suppliers</t>
-  </si>
-  <si>
-    <t>other energy suppliers</t>
+    <t>domestic industries</t>
   </si>
 </sst>
 </file>
@@ -184,18 +142,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -211,20 +163,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -564,64 +519,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" location="P587_26537" xr:uid="{BED49F6A-41C2-4620-8543-2B2BCC77744D}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -630,180 +591,153 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="4"/>
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>76843.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B15" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>1077.932</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B16">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>6388.31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>3170.51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>785.92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>12344.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>1077.932</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>12344.74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16">
-        <v>13422.672</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19">
-        <v>66475</v>
-      </c>
-      <c r="C19" s="5">
-        <f>B19/B22</f>
-        <v>0.98404215948958595</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20">
-        <v>1078</v>
-      </c>
-      <c r="C20" s="5">
-        <f>B20/B22</f>
-        <v>1.5957840510414045E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22">
-        <f>SUM(B19:B21)</f>
-        <v>67553</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>23</v>
+      <c r="B18">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -812,89 +746,50 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3">
-        <f>Data!C19</f>
-        <v>0.98404215948958595</v>
+        <v>15</v>
+      </c>
+      <c r="B2" s="5">
+        <f>SUM(Data!B3,Data!B7)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
+        <v>0.42384105960264901</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="3">
-        <f>Data!C20</f>
-        <v>1.5957840510414045E-2</v>
+        <v>24</v>
+      </c>
+      <c r="B3" s="5">
+        <f>SUM(Data!B11,Data!B16,Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
+        <v>0.52814569536423839</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="B4" s="5">
+        <f>(Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
+        <v>4.8013245033112585E-2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="8">
+        <v>21</v>
+      </c>
+      <c r="B5">
         <v>0</v>
       </c>
     </row>

--- a/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
+++ b/InputData/land/FoFObE/Fraction of Forests Owned by Entity.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27930"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\land\FoFObE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deept\OneDrive\Desktop\Input Data for India 2.0\land\FoFObE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D0EA2B-02FF-453F-9596-BFD3D1EA0E4A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D1BBC6E8-B97F-4CCB-9CF9-2680728DCE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CECDAE7-D5B7-4684-A608-12EF96037DE3}"/>
   <bookViews>
-    <workbookView xWindow="9150" yWindow="690" windowWidth="29520" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="FoFObE" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -26,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>FoFObE Fraction of Forests Owned by Entity</t>
   </si>
@@ -41,73 +46,103 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>National Forest</t>
-  </si>
-  <si>
-    <t>Other public</t>
-  </si>
-  <si>
-    <t>Forest industry</t>
-  </si>
-  <si>
-    <t>Other private</t>
-  </si>
-  <si>
-    <t>Timber land</t>
-  </si>
-  <si>
-    <t>Reserved forest</t>
-  </si>
-  <si>
-    <t>Other forest</t>
-  </si>
-  <si>
-    <t>U.S.</t>
-  </si>
-  <si>
-    <t>Ownership of Forest Land (million hectares)</t>
-  </si>
-  <si>
-    <t>U.S. Forest Service</t>
-  </si>
-  <si>
-    <t>U.S. Forest Facts and Historical Trends</t>
-  </si>
-  <si>
-    <t>http://www.fia.fs.fed.us/library/briefings-summaries-overviews/docs/ForestFactsMetric.pdf</t>
-  </si>
-  <si>
-    <t>Page 6</t>
+    <t>Forests Owned By Entity</t>
+  </si>
+  <si>
+    <t>Food and Agriculture Organization of the United Nations</t>
+  </si>
+  <si>
+    <t>Ownership of Forests and Other Wooded Lands</t>
+  </si>
+  <si>
+    <t>http://www.fao.org/docrep/007/ae354e/AE354E10.htm#P587_26537</t>
+  </si>
+  <si>
+    <t>Table: Input for Global Reporting Table 2</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>We assume all privately owned land is owned by industry</t>
+  </si>
+  <si>
+    <t>Recorded Forest Land in "000" ha (2000)</t>
+  </si>
+  <si>
+    <t>Total Recorded Forest Land</t>
+  </si>
+  <si>
+    <t>Recorded Forest under Private Ownership</t>
+  </si>
+  <si>
+    <t>Public Owners of un-classed Forest</t>
+  </si>
+  <si>
+    <t>Forest Department</t>
+  </si>
+  <si>
+    <t>Revenue Department</t>
+  </si>
+  <si>
+    <t>Corporate/Communities</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Owners of un-classed Forest</t>
+  </si>
+  <si>
+    <t>Private Owners</t>
+  </si>
+  <si>
+    <t>Public Owners</t>
+  </si>
+  <si>
+    <t>Type of Ownership</t>
+  </si>
+  <si>
+    <t>hectares</t>
+  </si>
+  <si>
+    <t>percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public </t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other or Unspecified </t>
+  </si>
+  <si>
+    <t xml:space="preserve">An unclassed forest is defined as any forest land or waste land or any </t>
+  </si>
+  <si>
+    <t xml:space="preserve">other land “recorded” in land records as “forest” but not notified in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">government gazette as “reserved” or “protected” forests under </t>
+  </si>
+  <si>
+    <t>Indian Forest Act.</t>
+  </si>
+  <si>
+    <t>Fraction of Forest Owned (dimensionless)</t>
   </si>
   <si>
     <t>government</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>The amount of government-owned forest is provided in the table.</t>
-  </si>
-  <si>
-    <t>We assume that all privately-owned forest used for timber land is owned</t>
-  </si>
-  <si>
-    <t>by industry, and half of the remaining privately-owned forest land is owned</t>
-  </si>
-  <si>
-    <t>by industry.  The remainder is owned by consumers.</t>
+    <t>domestic industries</t>
+  </si>
+  <si>
+    <t>labor and consumers</t>
   </si>
   <si>
     <t>foreign entities</t>
-  </si>
-  <si>
-    <t>labor and consumers</t>
-  </si>
-  <si>
-    <t>Fraction of Forest Owned (dimensionless)</t>
-  </si>
-  <si>
-    <t>domestic industries</t>
   </si>
 </sst>
 </file>
@@ -117,7 +152,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,12 +177,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -163,23 +204,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -199,9 +237,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -239,9 +277,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -274,26 +312,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -326,26 +347,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -519,70 +523,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>20</v>
+      <c r="B3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="2">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B7" r:id="rId1" location="P587_26537" xr:uid="{BED49F6A-41C2-4620-8543-2B2BCC77744D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
@@ -591,153 +589,180 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="38.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>7</v>
+      <c r="B3">
+        <v>76843.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
       </c>
       <c r="B5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>1077.932</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>13</v>
       </c>
       <c r="B8">
+        <v>6388.31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>3170.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>785.92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>12344.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>1077.932</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>12344.74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>13422.672</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1">
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>66475</v>
+      </c>
+      <c r="C19" s="5">
+        <f>B19/B22</f>
+        <v>0.98404215948958595</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>1078</v>
+      </c>
+      <c r="C20" s="5">
+        <f>B20/B22</f>
+        <v>1.5957840510414045E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <f>SUM(B19:B21)</f>
+        <v>67553</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18">
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -746,54 +771,239 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30">
       <c r="B1" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="5">
-        <f>SUM(Data!B3,Data!B7)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
-        <v>0.42384105960264901</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3">
+        <f>Data!C19</f>
+        <v>0.98404215948958595</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="5">
-        <f>SUM(Data!B11,Data!B16,Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
-        <v>0.52814569536423839</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3">
+        <f>Data!C20</f>
+        <v>1.5957840510414045E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="5">
-        <f>(Data!B18/2)/SUM(Data!B3,Data!B7,Data!B11,Data!B15)</f>
-        <v>4.8013245033112585E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5">
+        <v>34</v>
+      </c>
+      <c r="B5" s="8">
         <v>0</v>
       </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" s="8"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="8"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" s="8"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49666BF7-0782-42CB-A5FE-9F1582BF111C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB7258CB-F078-448B-9BD9-B7CFA16B8EF2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F830EF8-C0CA-4C7B-A1C5-20BA73364BFF}"/>
 </file>